--- a/test-data/accounttestdata.xlsx
+++ b/test-data/accounttestdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nazrinasari/Documents/automation/playwright2/test-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6283944-A45D-7C4A-ABE8-7190ADEB985A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2153A1D0-B2EA-A049-850D-1FB8BE176E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
   <si>
     <t>Environment</t>
   </si>
@@ -110,6 +110,12 @@
   </si>
   <si>
     <t>Yishun Singapore 20241212</t>
+  </si>
+  <si>
+    <t>https://staging.automationexercise.com/</t>
+  </si>
+  <si>
+    <t>https://prod.automationexercise.com/</t>
   </si>
 </sst>
 </file>
@@ -569,7 +575,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -619,12 +625,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
@@ -669,12 +675,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>1</v>
+      <c r="B4" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
@@ -723,6 +729,8 @@
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{F84E1EAF-0AE8-A247-930E-8E73F11416A4}"/>
     <hyperlink ref="C2" r:id="rId2" xr:uid="{403A3E1A-76B9-0745-84B2-E23D72C9F504}"/>
+    <hyperlink ref="B3" r:id="rId3" xr:uid="{F34729A2-0E8E-6249-A8D9-424903279800}"/>
+    <hyperlink ref="B4" r:id="rId4" xr:uid="{7609F25A-C9B9-AE46-B324-AF206A9EDE1D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
